--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\לימודים הנדסת תוכנה\שנה ג סמסטר ב\שיטות הנדסיות\פרויקט\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\almo1\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599D5F61-6583-4899-839E-DE102B77A352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0673A816-B5C5-4248-8DD8-DE2382FF91CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="11925" windowHeight="12863" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="159">
   <si>
     <t>Req. number</t>
   </si>
@@ -63,30 +63,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>User is defined in DB.</t>
-  </si>
-  <si>
-    <t>LoginSuccessful</t>
-  </si>
-  <si>
-    <t>Open "LogIN" window. Type a user ID: 2345236 Type a password: alex124 Click "OK" button.</t>
-  </si>
-  <si>
-    <t>The password is correct.</t>
-  </si>
-  <si>
-    <t>User logs in. System defines in DB the status of user 2345236 as logged-in.</t>
-  </si>
-  <si>
-    <t>LoginNonexistingUser</t>
-  </si>
-  <si>
-    <t>. . .</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> . . .</t>
-  </si>
-  <si>
     <t>NFR</t>
   </si>
   <si>
@@ -328,13 +304,318 @@
   </si>
   <si>
     <t>The segmentation report will be shown as a graph</t>
+  </si>
+  <si>
+    <t>IdentificationSuccessful_AsNonEmployee</t>
+  </si>
+  <si>
+    <t>Open login page.
+Click "Visitor Log In" button.
+Enter reservation number: 1234
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>The system logs the vistor in.</t>
+  </si>
+  <si>
+    <t>The system is on the log in page.
+There is a reservation number 1234 in the DB.</t>
+  </si>
+  <si>
+    <t>Regular visitor log in using reservation number.</t>
+  </si>
+  <si>
+    <t>IdentificationSuccessful_AsEmployee</t>
+  </si>
+  <si>
+    <t>Open login page.
+Click "Employee Log In" button.
+Enter user name: employeeTest.
+Enter password: employeeTest.
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>The system logs the employee in.</t>
+  </si>
+  <si>
+    <t>The system is on the log in page.
+There is an employee user in the DB.</t>
+  </si>
+  <si>
+    <t>Regular employee log in using his log in credentials.</t>
+  </si>
+  <si>
+    <t>IdentificationUnsuccessful_AsEmployee_WrongPassword</t>
+  </si>
+  <si>
+    <t>Open login page.
+Click "Employee Log In" button.
+Enter user name: employeeTest.
+Enter password: employeeTestFail.
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>The system displays the message "Wrong login credentials".
+The system will not log the user in.</t>
+  </si>
+  <si>
+    <t>The system is on the log in page.
+There is no employee user with these credentials in the DB.</t>
+  </si>
+  <si>
+    <t>Regular failed attempt to log an employee in.</t>
+  </si>
+  <si>
+    <t>IdentificationUnsuccessful_AsEmployee_WrongUsername</t>
+  </si>
+  <si>
+    <t>Open login page.
+Click "Employee Log In" button.
+Enter user name: employeeTestFail.
+Enter password: employeeTest.
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>IdentificationUnsuccessful_AsEmployee_WrongUsernameAndPassword</t>
+  </si>
+  <si>
+    <t>Open login page.
+Click "Employee Log In" button.
+Enter user name: employeeTestFail.
+Enter password: employeeTestFail.
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>IdentificationUnsuccessful_AsNonEmployee</t>
+  </si>
+  <si>
+    <t>Open login page.
+Click "Visitor Log In" button.
+Enter reservation number: 0000
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>The system displays the message "Wrong reservation number ".
+The system will not log the user in.</t>
+  </si>
+  <si>
+    <t>The system is on the log in page.
+There is no reservation number 0000 in the DB.</t>
+  </si>
+  <si>
+    <t>Regular failed attempt to log a visitor in.</t>
+  </si>
+  <si>
+    <t>UnsuccessfulBooking_AmountOfVisitorsEqualsZero</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 0
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button</t>
+  </si>
+  <si>
+    <t>The system displays the message "Number of visitors are not allowd. Must be 1 or more visitors".
+The system will not create the reservation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The user successfully logged in.
+</t>
+  </si>
+  <si>
+    <t>Booking requireing a minimum of 1 visitor.</t>
+  </si>
+  <si>
+    <t>UnsuccessfulBooking_NegativeAmountOfVisitors</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: -1
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button</t>
+  </si>
+  <si>
+    <t>UnsuccessfulBooking_TooMuchVisitors</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 16
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button</t>
+  </si>
+  <si>
+    <t>The system displays the message "Maximum visitors allowed are 15 ".
+The system will not create the reservation.</t>
+  </si>
+  <si>
+    <t>The user successfully logged in.
+There is a spot availble for more than 15 people at the time chose.</t>
+  </si>
+  <si>
+    <t>Max visitors allowed are 15.</t>
+  </si>
+  <si>
+    <t>RegularVisitorBooksAnOrginizedVisit_Fails</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 10
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button</t>
+  </si>
+  <si>
+    <t>The system will not create the reservation.
+The system will display a message "This ID is not registered as a guide".</t>
+  </si>
+  <si>
+    <t>The user is not registered as a guide in the DB.
+There is a spot for the number of people at the given time.</t>
+  </si>
+  <si>
+    <t>A regular visitor can't book an organized tour.</t>
+  </si>
+  <si>
+    <t>GroupVisitRegisteredAsGroupVisit</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter guide ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 10
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button
+Open reservation invoice</t>
+  </si>
+  <si>
+    <t>The system will display the reservation invoice and will say "Organized Group Visit" at the headline.</t>
+  </si>
+  <si>
+    <t>There is a user registered as a guide in the DB.
+There is a spot for the number of people at the given time.</t>
+  </si>
+  <si>
+    <t>A guige can book an organized tour.</t>
+  </si>
+  <si>
+    <t>RegisteringAVisitorAsAGuide_Fails</t>
+  </si>
+  <si>
+    <t>Open "Tour Guides" screen
+Click "Add New Tour Guide".
+Enter guide credintials.
+Click "OK" button.
+Open "Tour Guides" screen</t>
+  </si>
+  <si>
+    <t>The system will display a message "Tour guide already exists".
+The new tour guide will be visble in the "Tour Guide" screen.</t>
+  </si>
+  <si>
+    <t>Guide alreadty exists in DB.</t>
+  </si>
+  <si>
+    <t>Trying to add a guide that already exists</t>
+  </si>
+  <si>
+    <t>RegisteringAVisitorAsAGuide</t>
+  </si>
+  <si>
+    <t>The system will display a message "Tour guide added succssfuly".
+The new tour guide will be visble in the "Tour Guide" screen.</t>
+  </si>
+  <si>
+    <t>Guide does not alreadty exists in DB.</t>
+  </si>
+  <si>
+    <t>Trying to add a new guide</t>
+  </si>
+  <si>
+    <t>MessageSent_AfterAutomaticCancellation</t>
+  </si>
+  <si>
+    <t>Visitor recieves confirmation SMS and Email.
+Visitor will ignore the messages for 2 hours.
+Visitor will receive a cancellation message.</t>
+  </si>
+  <si>
+    <t>The system will send an Email and SMS so the visitor can confirm his visit. After 2 hours with no confirmation the system will cancel the reservation and will send another SMS and Email regarding the cancellation.</t>
+  </si>
+  <si>
+    <t>There is a reservation in the DB.
+The user ignores the first SMS and Email.</t>
+  </si>
+  <si>
+    <t>Checking that the cancellation message Is sent.</t>
+  </si>
+  <si>
+    <t>VisitorEnteringWaitingList_AsRegularVisitor</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 10
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button
+(System will display a message saying that the park is full. User will have 2 options:
+1.See availble spots.
+2.Enter waiting list).
+Click "Enter waiting list" button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system will desplay the message "Sorry, park is full. You can enter waiting list or choose another time".
+</t>
+  </si>
+  <si>
+    <t>The visitor logged in succssefuly.
+There is no spots for this group at that time.</t>
+  </si>
+  <si>
+    <t>Checking that a visitor can enter waiting line.</t>
+  </si>
+  <si>
+    <t>VisitorEnteringWaitingList_AsTourGuide</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter guide ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 10
+Enter e-mail: visitor@gmail.com
+Click "Book Visit" button
+(System will display a message saying that the park is full. User will have 2 options:
+1.See availble spots.
+2.Enter waiting list).
+Click "Enter waiting list" button.</t>
+  </si>
+  <si>
+    <t>The giude logged in succssefuly.
+There is no spots for this group at that time.</t>
+  </si>
+  <si>
+    <t>Checking that a guide can enter waiting line.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,6 +666,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -427,19 +715,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -453,6 +735,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +768,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -774,14 +1065,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.4375" customWidth="1"/>
-    <col min="2" max="2" width="88.0625" customWidth="1"/>
-    <col min="3" max="3" width="5.1875" customWidth="1"/>
+    <col min="1" max="1" width="9.5" customWidth="1"/>
+    <col min="2" max="2" width="88.125" customWidth="1"/>
+    <col min="3" max="3" width="5.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="135.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,884 +1083,884 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="6">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.4">
-      <c r="A17" s="6">
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1680,17 +1971,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.875" customWidth="1"/>
-    <col min="2" max="2" width="27.6875" customWidth="1"/>
+    <col min="1" max="1" width="79.75" customWidth="1"/>
+    <col min="2" max="2" width="27.75" customWidth="1"/>
     <col min="3" max="3" width="39.25" customWidth="1"/>
     <col min="4" max="4" width="24.75" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1707,50 +1998,277 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" ht="60.4" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="8" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="6" spans="1:5" ht="13.9" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:5" ht="15.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="2"/>
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="143.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="214.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="214.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>158</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1761,16 +2279,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F57B142-739C-42E7-8832-36341E864322}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="55.1875" customWidth="1"/>
-    <col min="2" max="2" width="32.5625" customWidth="1"/>
+    <col min="1" max="1" width="55.25" customWidth="1"/>
+    <col min="2" max="2" width="32.625" customWidth="1"/>
     <col min="3" max="3" width="51.625" customWidth="1"/>
     <col min="4" max="4" width="34.625" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1787,93 +2305,93 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1" ht="83.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" ht="83.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" s="3" customFormat="1" ht="83.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" ht="83.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" s="8" customFormat="1" ht="84.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" s="8" customFormat="1" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" s="8" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" s="8" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" s="8" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="79.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="5"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="73.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="5"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="78.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="42.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:5" ht="76.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:5" ht="15.4" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C16" s="7"/>
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" s="6" customFormat="1" ht="84.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" s="6" customFormat="1" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="79.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="73.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="78.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="42.4" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:5" ht="76.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1884,7 +2402,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD60C334-447E-4123-A1B5-2C4F489DB128}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\almo1\GoNature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reutd\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0673A816-B5C5-4248-8DD8-DE2382FF91CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322FDECC-3AFE-4714-926F-BB0E86C10215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="256">
   <si>
     <t>Req. number</t>
   </si>
@@ -610,12 +610,414 @@
   <si>
     <t>Checking that a guide can enter waiting line.</t>
   </si>
+  <si>
+    <t>ChangeCapacityRequestGapSuccessful</t>
+  </si>
+  <si>
+    <t>Park manager presses "change capacity"
+chooses park: "Banias Nature Reserve"
+sets capacity= "200"
+presses "Send request"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A request is sent for the department manager's approval and the message "Request Sent" is displayed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The manager is registered as the park manager and the parks capacity is already defined </t>
+  </si>
+  <si>
+    <t>Successful capacity change request</t>
+  </si>
+  <si>
+    <t>ChangeCapacityRequestUnSuccessfulNegative</t>
+  </si>
+  <si>
+    <t>Park manager presses "change capacity"
+chooses park: "Banias Nature Reserve"
+set capacity= "-200"
+presses "Send request"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system will not send a request to the department manager and the message "Invalid capacity" is displayed
+</t>
+  </si>
+  <si>
+    <t>UnSuccessful capacity change request (negative)</t>
+  </si>
+  <si>
+    <t>ConfirmCapacityChangeSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager presses "Capacity change requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested capacity: 200
+current capacity: 300 
+ manager presses "confirm request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve capacity changed to 200 and the message "Request confirmed" is displayed
+</t>
+  </si>
+  <si>
+    <t>The manager is registered as the department manager and a capacity change request was sent</t>
+  </si>
+  <si>
+    <t>Successful capacity change request confrmation</t>
+  </si>
+  <si>
+    <t>RejectCapacityChangeSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager presses "Capacity change requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested capacity: 200
+current capacity: 300 
+ manager presses "reject request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve capacity remains to 300 and the message "Request rejected" is displayed
+</t>
+  </si>
+  <si>
+    <t>Successful capacity change request rejection</t>
+  </si>
+  <si>
+    <t>DefineQuotaCapacityGapRequestSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager presses "define wanted capacity-qouta gap". 
+chooses park: "Banias Nature Reserve"
+The park's capacity= 200 
+Manager defines the gap to be 50   </t>
+  </si>
+  <si>
+    <t>A request is sent for the department manager's approval and the message "Request Sent" is displayed</t>
+  </si>
+  <si>
+    <t>Successful gap definition request</t>
+  </si>
+  <si>
+    <t>DefineQuotaCapacityGapUnSuccessfulNegative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager presses "define wanted capacity-qouta gap".
+chooses park: "Banias Nature Reserve" 
+The park's capacity= 200 
+Manager defines the gap to be -50
+presses "Send request"   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system will not send a request to the department manager and the message "Invalid gap value" is displayed
+</t>
+  </si>
+  <si>
+    <t>UnSuccessful gap definition request (negative gap)</t>
+  </si>
+  <si>
+    <t>DefineQuotaCapacityGapUnSuccessfulLargerThanCapacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager presses "define wanted capacity-qouta gap".
+chooses park: "Banias Nature Reserve" 
+The park's capacity= 200 
+Manager defines the gap= 250
+presses "Send request"   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The manager is registered as the park manager and the parks capacity and quota - capacity gap are already defined </t>
+  </si>
+  <si>
+    <t>UnSuccessful gap definition request (gap bigger than the defined capacity)</t>
+  </si>
+  <si>
+    <t>ConfirmGapDefinitionSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager presses "Quota - capacity gap definition requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested gap: 200  
+manager presses "confirm request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve quota - capacity gap defined to 200 and the message "Request confirmed" is displayed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The manager is registered as the department manager and a quota- capacity gap definition request was sent  </t>
+  </si>
+  <si>
+    <t>Successful gap definition request confirmation</t>
+  </si>
+  <si>
+    <t>RejectGapDefinitionSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager presses "Quota - capacity gap definition requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested gap: 200  
+manager presses "reject request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve quota - capacity gap remains undefined and the message "Request rejected" is displayed
+</t>
+  </si>
+  <si>
+    <t>Successful gap definition request rejection</t>
+  </si>
+  <si>
+    <t>ChangeQuotaCapacityGapSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager presses "define wanted capacity-qouta gap".
+chooses park: "Banias Nature Reserve" 
+The park's capacity= 200
+ Manager sets the gap to 50 
+presses "Send request"  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system will not send a request to the department manager and the message "Invalid gap value" is displayed 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The manager is registered as the park manager and the parks capacity and gap are already defined </t>
+  </si>
+  <si>
+    <t>Successful gap change request</t>
+  </si>
+  <si>
+    <t>ChangeQuotaCapacityGapUnSuccessfulNegative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager signs in and presses "change capacity-qouta gap".
+chooses park: "Banias Nature Reserve" 
+The park's capacity= 200 
+Manager changes the gap = -50
+presses "Send request"   </t>
+  </si>
+  <si>
+    <t>UnSuccessful gap change request (negative gap)</t>
+  </si>
+  <si>
+    <t>ChangeQuotaCapacityGapUnSuccessfulLargerThanCapacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager signs in and presses "change capacity-qouta gap".
+chooses park: "Banias Nature Reserve" 
+The park's capacity= 200 
+Manager defines the gap to 250   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system will not confirm the change
+</t>
+  </si>
+  <si>
+    <t>UnSuccessful gap change request (gap bigger than the defined capacity)</t>
+  </si>
+  <si>
+    <t>ConfirmGapChangeSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager signs in and presses "Quota - capacity  gap change requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested gap: 200
+current gap: 300 
+manager presses "confirm request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve quota - capacity gap changed to 200 and the message "Request confirmed" is displayed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The manager is registered as the department manager and a quota- capacity gap change request was sent  </t>
+  </si>
+  <si>
+    <t>Successful gap change request confirmation</t>
+  </si>
+  <si>
+    <t>RejectGapChangeSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager signs in and presses "Quota - capacity  gap change requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested gap: 200
+current gap: 300 
+manager presses "reject request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve quota - capacity gap remains 300 and the message "Request rejectod" is displayed
+</t>
+  </si>
+  <si>
+    <t>Successful gap change request rejection</t>
+  </si>
+  <si>
+    <t>AvgStayTimeCalculation</t>
+  </si>
+  <si>
+    <t>????????????</t>
+  </si>
+  <si>
+    <t>ChangeEstimatedStayTimeRequestSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager presses "change estimated stay time ".
+chooses park: "Banias Nature Reserve" 
+current stay time: 2.5 hours
+wanted stay time: 3 hours
+presses "Send reqest"   </t>
+  </si>
+  <si>
+    <t>The manager is registered as the park manager</t>
+  </si>
+  <si>
+    <t>Successful estimated stay time change request</t>
+  </si>
+  <si>
+    <t>ChangeEstimatedStayTimeRequestUnSuccessfulNegative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park manager presses "change estimated stay time ".
+chooses park: "Banias Nature Reserve" 
+current stay time: 2.5 hours
+wanted stay time: -3 hours
+presses "Send reqest"   </t>
+  </si>
+  <si>
+    <t>The system will not send a request to the department manager and the message "Invalid stay time" is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsuccessful estimated stay time change request (negative) </t>
+  </si>
+  <si>
+    <t>ConfirmEstimatedStayTimeChangeSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager presses "estimated stay time change requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested stay time: 3   
+manager presses "confirm request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve estimated stay time changes to 3 hours and the message "Request confirmed" is displayed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The manager is registered as the department manager and an estimated stay time change request was sent  </t>
+  </si>
+  <si>
+    <t>Successful estimated stay time change approval</t>
+  </si>
+  <si>
+    <t>RejectEstimatedStayTimeChangeSuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department manager presses "estimated stay time change requests" and selects a request from the list, 
+the request opens:
+park: Banias Nature Reserve
+requested stay time: 3   
+manager presses "reject request"
+   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve estimated stay time doesn’t change and the message "Request rejected" is displayed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BookingCancled_SeeReservationTable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 3
+Enter e-mail: visitor@gmail.com
+Click "book visit" button
+Choose "Reservation Table"  
+</t>
+  </si>
+  <si>
+    <t>The system informs the user that no space is available for selected visit time.
+The system does not create a reservation.
+The system allows the user to see the resrvation table in order to choose another date or join the waiting list.</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+Banias Nature Reserve has no available capacity for 3 visitors on 15/04/2026 at 10:00.
+Banias Nature Reserve's capacity: 1000
+Qouta- capacity gap: 200
+There are already 800 spots booked for the mentioned time at the park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bookings quota reached, reseration cancle, users chooses to look at the reservations table </t>
+  </si>
+  <si>
+    <t>OrdererAprrovesReminder</t>
+  </si>
+  <si>
+    <t>Orderer "Israel Israeli" receives an 
+e-mail and SMS saying "Dear Israel Israeli, please approve your visit in Banias Nature Reserve tommorow at 2pm within the next 2 hours by pressing the link below….".
+Israel immediately sees and approves his visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system accepts the approval and won't aoutmatically cancel the reservation </t>
+  </si>
+  <si>
+    <t>The user's reservation exists in the system with the correct e-mail address and phone number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user receives a reminder to their visit tommorow and doesn't approve it before aoutomtic cancellation  </t>
+  </si>
+  <si>
+    <t>OrdererMissesReminderAutoCancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orderer "Israel Israeli" receives an 
+e-mail and SMS saying "Dear Israel Israeli, please approve your visit in Banias Nature Reserve tommorow at 2pm within the next 2 hours by pressing the link below….".
+Israel sees message 3 hours too late, and can't approve his visit  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system aoutmatically cancels the reservation two hours after he message was sent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">user receives a reminder to their visit tommorow and approves it before aoutomtic cancellation  </t>
+  </si>
+  <si>
+    <t>AutoCancelMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reservation was automatically canceled </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system sents the orderer a cancellation message by e-mail and SMS saying "Dear Traveler, due to reminder disapproval, we had to cancel your visit tommorow."  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reminder for a reservation wasn't approved in time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">automtic cancellation message sent   </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,6 +1075,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -688,7 +1105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -711,11 +1128,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -743,6 +1220,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1065,14 +1557,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1"/>
-    <col min="2" max="2" width="88.125" customWidth="1"/>
-    <col min="3" max="3" width="5.25" customWidth="1"/>
+    <col min="2" max="2" width="88.09765625" customWidth="1"/>
+    <col min="3" max="3" width="5.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1094,7 +1586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1105,7 +1597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1116,7 +1608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1127,7 +1619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1138,7 +1630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1149,7 +1641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1160,7 +1652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1171,7 +1663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1182,7 +1674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1193,7 +1685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1204,7 +1696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1215,7 +1707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1226,7 +1718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1237,7 +1729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1248,7 +1740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -1259,7 +1751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1270,7 +1762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1281,7 +1773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1292,7 +1784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1303,7 +1795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1314,7 +1806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1325,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1336,7 +1828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1347,7 +1839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1358,7 +1850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1369,7 +1861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1380,7 +1872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1391,7 +1883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1402,7 +1894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1413,7 +1905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1424,7 +1916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1435,7 +1927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1446,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1457,7 +1949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1468,7 +1960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1479,7 +1971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1490,7 +1982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1501,7 +1993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1512,7 +2004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1523,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1534,7 +2026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1545,7 +2037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1556,7 +2048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1567,7 +2059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1578,7 +2070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1589,7 +2081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1600,7 +2092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1611,7 +2103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1622,7 +2114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1633,7 +2125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1644,7 +2136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1655,7 +2147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1666,7 +2158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1677,7 +2169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1688,7 +2180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1699,7 +2191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1710,7 +2202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1721,7 +2213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1732,7 +2224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1743,7 +2235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1754,7 +2246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1765,7 +2257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1776,7 +2268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1787,7 +2279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1798,7 +2290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1809,7 +2301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1820,7 +2312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1831,7 +2323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1842,7 +2334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1853,7 +2345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1864,7 +2356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1875,7 +2367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1886,7 +2378,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1897,7 +2389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1908,7 +2400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1919,7 +2411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1930,7 +2422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1941,7 +2433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1952,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1971,17 +2463,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Z41"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="79.75" customWidth="1"/>
-    <col min="2" max="2" width="27.75" customWidth="1"/>
-    <col min="3" max="3" width="39.25" customWidth="1"/>
-    <col min="4" max="4" width="24.75" customWidth="1"/>
+    <col min="1" max="1" width="79.69921875" customWidth="1"/>
+    <col min="2" max="2" width="27.69921875" customWidth="1"/>
+    <col min="3" max="3" width="39.19921875" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1998,7 +2490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>90</v>
       </c>
@@ -2015,7 +2507,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>95</v>
       </c>
@@ -2032,7 +2524,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>100</v>
       </c>
@@ -2049,7 +2541,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>105</v>
       </c>
@@ -2066,7 +2558,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="97.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>107</v>
       </c>
@@ -2083,7 +2575,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>109</v>
       </c>
@@ -2100,7 +2592,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>114</v>
       </c>
@@ -2117,7 +2609,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>119</v>
       </c>
@@ -2134,7 +2626,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>121</v>
       </c>
@@ -2151,7 +2643,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>126</v>
       </c>
@@ -2168,7 +2660,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="143.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>131</v>
       </c>
@@ -2185,7 +2677,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>136</v>
       </c>
@@ -2202,7 +2694,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>141</v>
       </c>
@@ -2219,7 +2711,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>145</v>
       </c>
@@ -2236,7 +2728,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="214.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>150</v>
       </c>
@@ -2253,7 +2745,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="214.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>155</v>
       </c>
@@ -2269,6 +2761,492 @@
       <c r="E17" s="9" t="s">
         <v>158</v>
       </c>
+    </row>
+    <row r="18" spans="1:5" ht="88.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="90.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+    </row>
+    <row r="33" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="Y38" s="15"/>
+      <c r="Z38" s="15"/>
+    </row>
+    <row r="39" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+      <c r="Z39" s="15"/>
+    </row>
+    <row r="40" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+      <c r="Z40" s="15"/>
+    </row>
+    <row r="41" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
+      <c r="Y41" s="15"/>
+      <c r="Z41" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2279,16 +3257,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F57B142-739C-42E7-8832-36341E864322}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.25" customWidth="1"/>
-    <col min="2" max="2" width="32.625" customWidth="1"/>
-    <col min="3" max="3" width="51.625" customWidth="1"/>
-    <col min="4" max="4" width="34.625" customWidth="1"/>
+    <col min="1" max="1" width="55.19921875" customWidth="1"/>
+    <col min="2" max="2" width="32.59765625" customWidth="1"/>
+    <col min="3" max="3" width="51.59765625" customWidth="1"/>
+    <col min="4" max="4" width="34.59765625" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -2305,92 +3283,92 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" s="6" customFormat="1" ht="84.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" s="6" customFormat="1" ht="84.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" s="6" customFormat="1" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" s="6" customFormat="1" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5" ht="79.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="79.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" ht="73.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5" ht="78.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="78.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:5" ht="42.4" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:5" ht="76.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="42.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" ht="76.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C16" s="5"/>
     </row>
   </sheetData>
@@ -2402,7 +3380,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD60C334-447E-4123-A1B5-2C4F489DB128}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reutd\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322FDECC-3AFE-4714-926F-BB0E86C10215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5C69C1-929D-449B-ABE2-7CF698134464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="259">
   <si>
     <t>Req. number</t>
   </si>
@@ -867,9 +867,6 @@
     <t>AvgStayTimeCalculation</t>
   </si>
   <si>
-    <t>????????????</t>
-  </si>
-  <si>
     <t>ChangeEstimatedStayTimeRequestSuccessful</t>
   </si>
   <si>
@@ -1011,6 +1008,23 @@
   </si>
   <si>
     <t xml:space="preserve">automtic cancellation message sent   </t>
+  </si>
+  <si>
+    <t>Average Stay Time Calculation for Park Visitors</t>
+  </si>
+  <si>
+    <t>Enter the park visit history screen.
+Choose the following visits:
+1. A group of 5 people spent 2 hours at the park
+2. 1 person spent 8 hours at the park
+Press "Calculate average stay time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The message "Average stay time calculated: 3 hours" will appear  on the screen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A park exists in the system
+A few visits are recorded in the system (number of people and stay time for each reservation) </t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1188,11 +1202,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1235,6 +1260,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2467,7 +2495,7 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="79.69921875" customWidth="1"/>
-    <col min="2" max="2" width="27.69921875" customWidth="1"/>
+    <col min="2" max="2" width="36.8984375" customWidth="1"/>
     <col min="3" max="3" width="39.19921875" customWidth="1"/>
     <col min="4" max="4" width="24.69921875" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
@@ -2983,7 +3011,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="136.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>215</v>
       </c>
@@ -3000,117 +3028,123 @@
         <v>218</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="131.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
+      <c r="B32" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="33" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>179</v>
       </c>
       <c r="D33" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>223</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="C34" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="D34" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>227</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="C35" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="D35" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="E35" s="12" t="s">
         <v>232</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="C36" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>236</v>
-      </c>
       <c r="D36" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>232</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="C37" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>236</v>
-      </c>
       <c r="D37" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>232</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="C38" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="D38" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="E38" s="14" t="s">
         <v>240</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>241</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -3136,19 +3170,19 @@
     </row>
     <row r="39" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="C39" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="D39" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="E39" s="14" t="s">
         <v>245</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>246</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -3174,19 +3208,19 @@
     </row>
     <row r="40" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="C40" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="D40" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" s="14" t="s">
         <v>249</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>250</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
@@ -3212,19 +3246,19 @@
     </row>
     <row r="41" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="C41" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="D41" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="E41" s="14" t="s">
         <v>254</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>255</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>

--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reutd\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5C69C1-929D-449B-ABE2-7CF698134464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC66BB9-75FB-4E80-9ACE-AC56652F95A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
     <sheet name="TestCase" sheetId="2" r:id="rId2"/>
-    <sheet name="Search" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="260">
   <si>
     <t>Req. number</t>
   </si>
@@ -1026,12 +1024,20 @@
     <t xml:space="preserve">A park exists in the system
 A few visits are recorded in the system (number of people and stay time for each reservation) </t>
   </si>
+  <si>
+    <t xml:space="preserve">Group #1, members: 
+Bar Sagi, bar.sagi@e.braude.ac.il
+Shiraz Shamai, shiraz.shamai@e.braude.ac.il
+Gal Dolev, gal.dolev@e.braude.ac.il
+Reut Dahan, reut.dahan@e.braude.ac.il
+date: </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1052,22 +1058,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1225,20 +1215,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1247,24 +1231,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1"/>
@@ -1592,78 +1580,72 @@
     <col min="3" max="3" width="5.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" s="16" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -1671,21 +1653,21 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
@@ -1693,54 +1675,54 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
@@ -1748,10 +1730,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -1759,43 +1741,43 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>21</v>
       </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
@@ -1803,21 +1785,21 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -1825,21 +1807,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -1847,54 +1829,54 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -1902,109 +1884,109 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
@@ -2012,65 +1994,65 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -2078,32 +2060,32 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -2111,21 +2093,21 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
@@ -2133,10 +2115,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
         <v>3</v>
@@ -2144,32 +2126,32 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
@@ -2177,98 +2159,98 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
@@ -2276,21 +2258,21 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
@@ -2298,65 +2280,65 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
@@ -2364,10 +2346,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C71" t="s">
         <v>3</v>
@@ -2375,76 +2357,76 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>81</v>
       </c>
-      <c r="C74" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>74</v>
-      </c>
-      <c r="B76" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" t="s">
-        <v>3</v>
+      <c r="C75" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
         <v>3</v>
@@ -2452,21 +2434,21 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
         <v>9</v>
@@ -2474,16 +2456,30 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>80</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" t="s">
         <v>89</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C83" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2491,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:Z41"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="79.69921875" customWidth="1"/>
@@ -2501,921 +2497,797 @@
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="16" customFormat="1" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="4" spans="1:5" s="4" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="5" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="6" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="97.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="7" spans="1:5" ht="97.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="8" spans="1:5" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+    <row r="9" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+    <row r="10" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+    <row r="11" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+    <row r="12" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D12" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+    <row r="13" spans="1:5" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+    <row r="14" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E15" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+    <row r="16" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D16" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E16" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+    <row r="17" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D17" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+    <row r="18" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D18" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E18" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="88.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+    <row r="19" spans="1:5" ht="88.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B19" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C19" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D19" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E19" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="90.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+    <row r="20" spans="1:5" ht="90.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+    <row r="21" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C21" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E21" s="10" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+    <row r="22" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D22" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E22" s="10" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+    <row r="23" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C23" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D23" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E23" s="10" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+    <row r="24" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C24" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D24" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E24" s="10" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+    <row r="25" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C25" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D25" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E25" s="10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+    <row r="26" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D26" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E26" s="10" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+    <row r="27" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C27" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E27" s="10" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+    <row r="28" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C28" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D28" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E28" s="10" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+    <row r="29" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C29" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D29" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E29" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+    <row r="30" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C30" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D30" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E30" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+    <row r="31" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C31" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D31" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E31" s="10" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="136.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+    <row r="32" spans="1:5" ht="136.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C32" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D32" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E32" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="131.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
+    <row r="33" spans="1:26" ht="131.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B33" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C33" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D33" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E33" s="10" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+    <row r="34" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C34" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D34" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E34" s="10" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+    <row r="35" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C35" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D35" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E35" s="10" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+    <row r="36" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B36" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C36" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D36" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E36" s="10" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+    <row r="37" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C37" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D37" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E37" s="10" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+    <row r="38" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C38" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D38" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E38" s="10" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+    <row r="39" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="15"/>
-      <c r="Z38" s="15"/>
-    </row>
-    <row r="39" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+    </row>
+    <row r="40" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B40" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C40" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D40" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E40" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="15"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
-      <c r="Y39" s="15"/>
-      <c r="Z39" s="15"/>
-    </row>
-    <row r="40" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+      <c r="U40" s="13"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="13"/>
+      <c r="Z40" s="13"/>
+    </row>
+    <row r="41" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B41" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C41" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E41" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="15"/>
-      <c r="Z40" s="15"/>
-    </row>
-    <row r="41" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="13"/>
+      <c r="U41" s="13"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="13"/>
+      <c r="Z41" s="13"/>
+    </row>
+    <row r="42" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C42" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D42" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E42" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="15"/>
-      <c r="Z41" s="15"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+      <c r="P42" s="13"/>
+      <c r="Q42" s="13"/>
+      <c r="R42" s="13"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="13"/>
+      <c r="U42" s="13"/>
+      <c r="V42" s="13"/>
+      <c r="W42" s="13"/>
+      <c r="X42" s="13"/>
+      <c r="Y42" s="13"/>
+      <c r="Z42" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F57B142-739C-42E7-8832-36341E864322}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="55.19921875" customWidth="1"/>
-    <col min="2" max="2" width="32.59765625" customWidth="1"/>
-    <col min="3" max="3" width="51.59765625" customWidth="1"/>
-    <col min="4" max="4" width="34.59765625" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="83.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" s="6" customFormat="1" ht="84.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" s="6" customFormat="1" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" s="6" customFormat="1" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" ht="79.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" ht="78.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="42.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:5" ht="76.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD60C334-447E-4123-A1B5-2C4F489DB128}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reutd\GoNature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rygra\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC66BB9-75FB-4E80-9ACE-AC56652F95A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53314E48-F03D-4BD4-9D93-D158BE75C2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
+    <workbookView xWindow="1170" yWindow="495" windowWidth="22950" windowHeight="15705" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="344">
   <si>
     <t>Req. number</t>
   </si>
@@ -1032,16 +1032,424 @@
 Reut Dahan, reut.dahan@e.braude.ac.il
 date: </t>
   </si>
+  <si>
+    <t>CheckAvailableSpots_HasSpace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open "Availability" screen
+Select park : Banias Nature Reserve
+Select date &amp; time : 07/04/2026, 10:00
+</t>
+  </si>
+  <si>
+    <t>The system displays the exact number of available spots
+(e.g. "50 available spots")</t>
+  </si>
+  <si>
+    <t>Banias Nature Reserve has 50 available spots for 07/04/2026 at 10:00</t>
+  </si>
+  <si>
+    <t>checking that the system displays available spots correctly</t>
+  </si>
+  <si>
+    <t>CheckAvailableSpots_FullyBooked</t>
+  </si>
+  <si>
+    <t>Open "Availablity" screen
+Select park : Banias Nature Reserve
+Select date &amp; time : 07/04/2026, 14:00</t>
+  </si>
+  <si>
+    <t>The system displays "Fully Booked"</t>
+  </si>
+  <si>
+    <t>Banias Nature Reserve is fully booked  for 07/04/2026 at 14:00</t>
+  </si>
+  <si>
+    <t>checking display when park is fully booked</t>
+  </si>
+  <si>
+    <t>CheckAvailableSpots_PartialSpace</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Select park : Banias Nature Reserve
+Select date &amp; time : 08/04/2026, 10:00
+Enter number of visitors: 10
+Click "Book visit"</t>
+  </si>
+  <si>
+    <t>The system displays a warning message: "Only 5 spots left for this date &amp; time."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banias Nature Reserve has only 5 spots available for 08/04/2026, 10:00 </t>
+  </si>
+  <si>
+    <t>requesting more spots than currently available</t>
+  </si>
+  <si>
+    <t>ReportExit_Successful</t>
+  </si>
+  <si>
+    <t>Open "Occupancy Management" screen
+Enter number of exiting visitors: 4
+Click "Report Exit"</t>
+  </si>
+  <si>
+    <t>The system decreases the current park occupancy by 4
+A success message is displayed</t>
+  </si>
+  <si>
+    <t>Employee is logged in.
+Current park occupancy is at least 4</t>
+  </si>
+  <si>
+    <t>standard manual exit report.</t>
+  </si>
+  <si>
+    <t>ReportExit_ByGroupLeadID</t>
+  </si>
+  <si>
+    <t>Open "Occupancy Management" screen
+Click "Group Exit"
+Enter booking lead's ID number
+Click "Report Exit"</t>
+  </si>
+  <si>
+    <t>System updates the status of the entire group to "Exited".
+Park occupancy decreases by the number of visitors in that booking</t>
+  </si>
+  <si>
+    <t>Employee is logged in.
+a group associated with that ID is currently marked as "Inside Park".</t>
+  </si>
+  <si>
+    <t>Entering the group leader's ID on exit marks the whole group is exited and decreases the total number of visitors accordingly</t>
+  </si>
+  <si>
+    <t>Check the available spots in the park
+Perform exit report
+Check the available spots in the park (again)</t>
+  </si>
+  <si>
+    <t>The system accurately displays the number of visitors before the exit, and then after the group exits (e.g. 4 people) the number is decreased by 4.</t>
+  </si>
+  <si>
+    <t>Employee is logged in.
+Current park occupancy is at least 4 and a group of size 4 exists in the park</t>
+  </si>
+  <si>
+    <t>Verify system correctly calculates occupancy in real-time.</t>
+  </si>
+  <si>
+    <t>GenerateBill_PrebookedFamily</t>
+  </si>
+  <si>
+    <t>Open "Entrance Management" screen
+Click "Individual/Family visit" button
+Enter reservation ID
+Click "Generate Bill" button</t>
+  </si>
+  <si>
+    <t>System generates a bill with 15% discount.</t>
+  </si>
+  <si>
+    <t>A group associated with the 
+ID in the reservation exists</t>
+  </si>
+  <si>
+    <t>Pricing type 1</t>
+  </si>
+  <si>
+    <t>GenerateBill_CasualVisit</t>
+  </si>
+  <si>
+    <t>Open "Entrance Management" screen
+Click "Casual visit" button
+Select "Indiviual / Familiy"
+Enter number of visitors
+Click "Generate Bill" button</t>
+  </si>
+  <si>
+    <t>System generates bill at full price
+(no discount)</t>
+  </si>
+  <si>
+    <t>Availalble space for number of visitors</t>
+  </si>
+  <si>
+    <t>Pricing type 2</t>
+  </si>
+  <si>
+    <t>GenerateBill_PrebookedGroup_FrontalPay</t>
+  </si>
+  <si>
+    <t>Open "Entrance Management" screen
+Click "Group visit" button
+Enter reservation ID
+Click "Generate Bill" button</t>
+  </si>
+  <si>
+    <t>System generates a bill with 25% discount.
+Guide is charged 0. (Bill doesn’t include guide)</t>
+  </si>
+  <si>
+    <t>Pricing type 3 - frontal pay</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GenerateBill_PrebookedGroup_Prepay 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(לא בטוח לגבי זה)</t>
+    </r>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 16/04/2026 11:00
+Enter number of visitors: 12
+Enter e-mail: guide@gmail.com
+Click "book visit" button
+(?) Click "Prepay" button (?)</t>
+  </si>
+  <si>
+    <t>System generates a bill with 37% discount.
+Guide is charged 0. (Bill doesn’t include guide)</t>
+  </si>
+  <si>
+    <t>The group guide is registered in the system.
+Banias Nature Reserve has available capacity for 12 visitors on 16/04/2026 at 11:00.</t>
+  </si>
+  <si>
+    <t>Pricing type 3 - prepay</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GenerateBill_CasualGroup
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>לא סגור אם זה אפשרי בכלל בסיפור אבל נראלי שכן כי לא כתוב שלא (או ספספתי)</t>
+    </r>
+  </si>
+  <si>
+    <t>Open "Entrance Management" screen
+Click "Casual visit" button
+Select "Organized Group"
+Enter number of visitors
+Click "Generate Bill" button</t>
+  </si>
+  <si>
+    <t>System generates a bill with a discount of 10%.
+Guide is charged normally. (Bill includes guide)</t>
+  </si>
+  <si>
+    <t>The group guide is registered in the system.
+Available space for number of visitors</t>
+  </si>
+  <si>
+    <t>Pricing type 4</t>
+  </si>
+  <si>
+    <t>GenerateBill_Subscriber_CasualVisit</t>
+  </si>
+  <si>
+    <t>Open "Entrance Management" screen
+Click "Member visit" button
+Enter Subscriber ID
+Click "Identify visitor"
+Enter number of visitors
+Click "Generate Bill" button</t>
+  </si>
+  <si>
+    <t>System generates a bill applying 10% subscriber discount to the full regular price.</t>
+  </si>
+  <si>
+    <t>Visitor has an active subscriber status.
+No prior reservation exists.
+Park has available space.</t>
+  </si>
+  <si>
+    <t>Pricing type 5 - casual visit</t>
+  </si>
+  <si>
+    <t>GenerateBill_Subscriber_Prebooked</t>
+  </si>
+  <si>
+    <t>Open "Entrance Management" screen
+Click "Member visit" button
+Enter Subscriber ID
+Click "Identify visitor"
+System presents booking
+Click "Generate Bill" button</t>
+  </si>
+  <si>
+    <t>System generates bill applying multiple discounts : 15% (prebook) + 10% (subscriber).
+In total 25% discount</t>
+  </si>
+  <si>
+    <t>Visitor has an active subscriber status.
+A valid reservations for that visitor exists</t>
+  </si>
+  <si>
+    <t>Pricint type 5 - booked visit</t>
+  </si>
+  <si>
+    <t>GenerateReport_Visitor_Successful</t>
+  </si>
+  <si>
+    <t>Open "Reports" screen
+Select "Visitor Report".
+Select date : 04/2026
+Click "Generate Report"</t>
+  </si>
+  <si>
+    <t>System generates a report detailing entry times and stay durations,
+ segmented by individuals and organized groups.
+The report is presented as a visual/graphical representation.</t>
+  </si>
+  <si>
+    <t>User is logged in as a Department Manager.
+Database contains visitor entry/exit records for the selected month.</t>
+  </si>
+  <si>
+    <t>Generate visitor report for a 
+period with existing visitor activity.</t>
+  </si>
+  <si>
+    <t>GenerateReport_Visitor_Unsuccessful</t>
+  </si>
+  <si>
+    <t>Open "Reports" screen
+Select "Visitor Report".
+Select date : 04/2027
+Click "Generate Report"</t>
+  </si>
+  <si>
+    <t>System displays message
+"No data available for selected period".</t>
+  </si>
+  <si>
+    <t>User is logged in as a Department Manager.
+Database contains no visitor entry/exit records for the selected month.</t>
+  </si>
+  <si>
+    <t>Generate visitor report for a 
+period with no existing visitor activity.</t>
+  </si>
+  <si>
+    <t>RecordEntryTime_UponCheckin</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open "Entrance Management" screen
+Click "Individual/Family visit" button
+Enter reservation ID
+Click "Confirm Entry" button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Open visitor log or database record (?)</t>
+    </r>
+  </si>
+  <si>
+    <t>The system saves the exact time of the "Confirm Entry" action as the visitor's entry time.</t>
+  </si>
+  <si>
+    <t>Park employee is logged in.
+Visitor has a prepaid reservation.</t>
+  </si>
+  <si>
+    <t>Check if the system records the currect timestamp when a visitor enters</t>
+  </si>
+  <si>
+    <t>CalculateDuration_BasedOnEntryTime</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open "Exit Management" screen
+Click "Individual/Family visit" button
+Enter reservation ID
+Click "Confirm Exit" button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Open visitor log or database record (?)</t>
+    </r>
+  </si>
+  <si>
+    <t>The system correctly calculates the stay duration by subtracting the saved entry time from the current exit time.</t>
+  </si>
+  <si>
+    <t>Visitor is currently in the 
+park with previously recorded entry time</t>
+  </si>
+  <si>
+    <t>check if the system correctly caculates stay duration upon exit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(?)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CheckOccupancy_AfterExit</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1055,14 +1463,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1082,7 +1490,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1090,9 +1498,32 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1207,7 +1638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1246,13 +1677,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1276,7 +1720,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1573,11 +2017,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
   <dimension ref="A1:C83"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5" customWidth="1"/>
-    <col min="2" max="2" width="88.09765625" customWidth="1"/>
-    <col min="3" max="3" width="5.19921875" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="88.140625" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="16" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1585,7 +2029,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="121.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1618,7 +2062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1761,7 +2205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2487,22 +2931,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:Z42"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="79.69921875" customWidth="1"/>
-    <col min="2" max="2" width="36.8984375" customWidth="1"/>
-    <col min="3" max="3" width="39.19921875" customWidth="1"/>
-    <col min="4" max="4" width="24.69921875" customWidth="1"/>
+    <col min="1" max="1" width="79.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="16" customFormat="1" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="16" customFormat="1" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2519,7 +2963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>90</v>
       </c>
@@ -2553,7 +2997,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>100</v>
       </c>
@@ -2570,7 +3014,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>105</v>
       </c>
@@ -2587,7 +3031,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="97.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>107</v>
       </c>
@@ -2604,7 +3048,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>109</v>
       </c>
@@ -2621,7 +3065,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>114</v>
       </c>
@@ -2638,7 +3082,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>119</v>
       </c>
@@ -2655,7 +3099,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>121</v>
       </c>
@@ -2672,7 +3116,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="124.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>126</v>
       </c>
@@ -2689,7 +3133,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="138.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>131</v>
       </c>
@@ -2706,7 +3150,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>136</v>
       </c>
@@ -2723,7 +3167,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>141</v>
       </c>
@@ -2740,7 +3184,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="83.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>145</v>
       </c>
@@ -2757,7 +3201,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>150</v>
       </c>
@@ -2774,7 +3218,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="207.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>155</v>
       </c>
@@ -2791,7 +3235,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="88.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="88.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>159</v>
       </c>
@@ -2808,7 +3252,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="90.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>164</v>
       </c>
@@ -2825,7 +3269,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="157.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>168</v>
       </c>
@@ -2842,7 +3286,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="157.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="157.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>173</v>
       </c>
@@ -2859,7 +3303,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>177</v>
       </c>
@@ -2876,7 +3320,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>181</v>
       </c>
@@ -2893,7 +3337,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>185</v>
       </c>
@@ -2910,7 +3354,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>189</v>
       </c>
@@ -2927,7 +3371,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>194</v>
       </c>
@@ -2944,7 +3388,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>198</v>
       </c>
@@ -2961,7 +3405,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="135.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>203</v>
       </c>
@@ -2978,7 +3422,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>206</v>
       </c>
@@ -2995,7 +3439,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>210</v>
       </c>
@@ -3012,7 +3456,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="136.80000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="136.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>215</v>
       </c>
@@ -3029,7 +3473,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="131.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="131.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>219</v>
       </c>
@@ -3046,7 +3490,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>220</v>
       </c>
@@ -3063,7 +3507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="120.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>224</v>
       </c>
@@ -3080,7 +3524,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>228</v>
       </c>
@@ -3097,7 +3541,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>233</v>
       </c>
@@ -3114,7 +3558,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>233</v>
       </c>
@@ -3131,7 +3575,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>236</v>
       </c>
@@ -3169,7 +3613,7 @@
       <c r="Y39" s="13"/>
       <c r="Z39" s="13"/>
     </row>
-    <row r="40" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>241</v>
       </c>
@@ -3207,7 +3651,7 @@
       <c r="Y40" s="13"/>
       <c r="Z40" s="13"/>
     </row>
-    <row r="41" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>246</v>
       </c>
@@ -3245,7 +3689,7 @@
       <c r="Y41" s="13"/>
       <c r="Z41" s="13"/>
     </row>
-    <row r="42" spans="1:26" ht="169.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>250</v>
       </c>
@@ -3283,6 +3727,315 @@
       <c r="Y42" s="13"/>
       <c r="Z42" s="13"/>
     </row>
+    <row r="43" spans="1:26" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A55" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A59" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+    </row>
+    <row r="61" spans="1:5" ht="126" x14ac:dyDescent="0.25">
+      <c r="A61" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="126" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>342</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:XFD1"/>

--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rygra\GoNature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shiraz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53314E48-F03D-4BD4-9D93-D158BE75C2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863D3C4A-FF0E-4DDF-A332-A3C49C38BC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="495" windowWidth="22950" windowHeight="15705" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="17287" windowHeight="11527" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="426">
   <si>
     <t>Req. number</t>
   </si>
@@ -1197,22 +1197,6 @@
     <t>Pricing type 3 - frontal pay</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">GenerateBill_PrebookedGroup_Prepay 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(לא בטוח לגבי זה)</t>
-    </r>
-  </si>
-  <si>
     <t>Open booking screen
 Enter visitor ID
 Select park: Banias Nature Reserve
@@ -1234,22 +1218,6 @@
     <t>Pricing type 3 - prepay</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">GenerateBill_CasualGroup
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>לא סגור אם זה אפשרי בכלל בסיפור אבל נראלי שכן כי לא כתוב שלא (או ספספתי)</t>
-    </r>
-  </si>
-  <si>
     <t>Open "Entrance Management" screen
 Click "Casual visit" button
 Select "Organized Group"
@@ -1356,6 +1324,29 @@
   </si>
   <si>
     <t>RecordEntryTime_UponCheckin</t>
+  </si>
+  <si>
+    <t>The system saves the exact time of the "Confirm Entry" action as the visitor's entry time.</t>
+  </si>
+  <si>
+    <t>Park employee is logged in.
+Visitor has a prepaid reservation.</t>
+  </si>
+  <si>
+    <t>Check if the system records the currect timestamp when a visitor enters</t>
+  </si>
+  <si>
+    <t>CalculateDuration_BasedOnEntryTime</t>
+  </si>
+  <si>
+    <t>The system correctly calculates the stay duration by subtracting the saved entry time from the current exit time.</t>
+  </si>
+  <si>
+    <t>Visitor is currently in the 
+park with previously recorded entry time</t>
+  </si>
+  <si>
+    <t>check if the system correctly caculates stay duration upon exit</t>
   </si>
   <si>
     <r>
@@ -1367,7 +1358,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
@@ -1375,19 +1365,6 @@
       </rPr>
       <t>Open visitor log or database record (?)</t>
     </r>
-  </si>
-  <si>
-    <t>The system saves the exact time of the "Confirm Entry" action as the visitor's entry time.</t>
-  </si>
-  <si>
-    <t>Park employee is logged in.
-Visitor has a prepaid reservation.</t>
-  </si>
-  <si>
-    <t>Check if the system records the currect timestamp when a visitor enters</t>
-  </si>
-  <si>
-    <t>CalculateDuration_BasedOnEntryTime</t>
   </si>
   <si>
     <r>
@@ -1399,7 +1376,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
@@ -1409,20 +1385,10 @@
     </r>
   </si>
   <si>
-    <t>The system correctly calculates the stay duration by subtracting the saved entry time from the current exit time.</t>
-  </si>
-  <si>
-    <t>Visitor is currently in the 
-park with previously recorded entry time</t>
-  </si>
-  <si>
-    <t>check if the system correctly caculates stay duration upon exit</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="14"/>
         <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -1432,7 +1398,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="14"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -1440,16 +1406,420 @@
       <t xml:space="preserve"> CheckOccupancy_AfterExit</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GenerateBill_PrebookedGroup_Prepay 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(לא בטוח לגבי זה)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GenerateBill_CasualGroup
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>לא סגור אם זה אפשרי בכלל בסיפור אבל נראלי שכן כי לא כתוב שלא (או ספספתי)</t>
+    </r>
+  </si>
+  <si>
+    <t>BookVisitSuccessful_Available</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 3
+Enter e-mail: visitor@gmail.com
+Click "book visit" button</t>
+  </si>
+  <si>
+    <t>The system creates a reservation for Banias Nature Reserve on 15/04/2026 at 10:00 for 3 visitors.
+The system displays a booking confirmation massage.
+The system sends a confirmation to visitor@gmail.com</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+Banias Nature Reserve has available capacity for 3 visitors on 15/04/2026 at 10:00.</t>
+  </si>
+  <si>
+    <t>Regular visitor booking</t>
+  </si>
+  <si>
+    <t>BookVisitUnsuccessful_NotAvailable</t>
+  </si>
+  <si>
+    <t>The system informs the user that no space is available for selected visit time.
+The system does not create a reservation.
+The system allows the user to choose another date or join the waiting list.</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+Banias Nature Reserve has no available capacity for 3 visitors on 15/04/2026 at 10:00.</t>
+  </si>
+  <si>
+    <t>Park is fully booked</t>
+  </si>
+  <si>
+    <t>BookVisitWaitingList</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 3
+Enter e-mail: visitor@gmail.com
+Click "book visit" button
+Choose "join waiting list"</t>
+  </si>
+  <si>
+    <t>The system adds the user to the waiting list for Banias Nature Reserve on 15/04/2026 at 10:00.
+The system displays a waiting list confirmation message</t>
+  </si>
+  <si>
+    <t>User joins waiting list</t>
+  </si>
+  <si>
+    <t>BookVisitOrganizedGroupSuccessful</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 16/04/2026 11:00
+Enter number of visitors: 12
+Enter e-mail: guide@gmail.com
+Click "book visit" button</t>
+  </si>
+  <si>
+    <t>The system creates a group reservation for Banias Nature Reserve on 16/04/2026 at 11:00 for 12 visitors.
+The system displays a booking confirmation massage.
+The system sends a confirmation to guide@gmail.com</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+The group guide is registered in the system.
+Banias Nature Reserve has available capacity for 12 visitors on 16/04/2026 at 11:00.</t>
+  </si>
+  <si>
+    <t>Organized group booking</t>
+  </si>
+  <si>
+    <t>BookVisitPrivateGroupSuccessful</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 16/04/2026 11:00
+Enter number of visitors: 4
+Enter e-mail: guide2@gmail.com
+Click "book visit" button</t>
+  </si>
+  <si>
+    <t>The system creates a group reservation for Banias Nature Reserve on 16/04/2026 at 11:00 for 4 visitors.
+The system displays a booking confirmation massage.
+The system sends a confirmation to guide2@gmail.com</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+The group guide is registered in the system.
+Banias Nature Reserve has available capacity for 4 visitors on 16/04/2026 at 11:00.</t>
+  </si>
+  <si>
+    <t>Organized private group booking</t>
+  </si>
+  <si>
+    <t>ConfirmVisitSuccessful</t>
+  </si>
+  <si>
+    <t>Open reservation confirmation message
+Enter visitor ID
+Select reservation for Banias Nature Reserve on 15/04/2026 at 10:00
+Click "confirm visit" button</t>
+  </si>
+  <si>
+    <t>The system updates the reservation status to "confirmed".
+The system displays a confirmation message.</t>
+  </si>
+  <si>
+    <t>The system is on the reservation confirmation screen.
+A reservation for Banias Nature Reserve on 15/04/2026 at 10:00 exists in the system.
+The reminder message was sent to the visitor.</t>
+  </si>
+  <si>
+    <t>Visitor confirms reservation after reminder</t>
+  </si>
+  <si>
+    <t>CancelReservationSuccessful</t>
+  </si>
+  <si>
+    <t>Open reservation confirmation message
+Enter visitor ID
+Select reservation for Banias Nature Reserve on 15/04/2026 at 10:00
+Click "cancel reservation" button</t>
+  </si>
+  <si>
+    <t>The system cancel the reservation.
+The system displays a cancellation message.
+The cancelled place become available in the system.</t>
+  </si>
+  <si>
+    <t>The system is on the reservation management screen.
+A valid reservation for Banias Nature Reserve on 15/04/2026 at 10:00 exists in the system.</t>
+  </si>
+  <si>
+    <t>Visitor cancels existing reservation</t>
+  </si>
+  <si>
+    <t>WaitingListNotificationSent</t>
+  </si>
+  <si>
+    <t>Open waiting list management screen.
+Enter visitor ID who has an existing reservation.
+Select reservation for Banias Nature Reserve on 15/04/2026 at 10:00.
+Click "cancel reservation" button.</t>
+  </si>
+  <si>
+    <t>The system sends an available notification to the first visitor on the waiting list.
+The notification is related to Banias Nature Reserve on 15/04/2026 at 10:00.</t>
+  </si>
+  <si>
+    <t>A valid reservation for Banias Nature Reserve on 15/04/2026 at 10:00 exists in the system.
+A waiting list exists for Banias Nature Reserve on 15/04/2026 at 10:00.
+At least one visitor is registered in the waiting list.</t>
+  </si>
+  <si>
+    <t>Notification to the first visitor in the waiting list</t>
+  </si>
+  <si>
+    <t>WaitingListSpotReservedForOneHour</t>
+  </si>
+  <si>
+    <t>Open waiting list confirmation screen
+Enter visitor ID of the first visitor on the waiting list
+Select the available visit for Banias Nature Reserve on 15/04/2026 at 10:00
+Do not click "confirm visit" button for one hour</t>
+  </si>
+  <si>
+    <t>The system reserves the available spot for the first visitor on the waiting list for one hour.
+The spot is not assigned to another visitor during that hour.</t>
+  </si>
+  <si>
+    <t>A spot became available for Banias Nature Reserve on 15/04/2026 at 10:00.
+A waiting list exists for Banias Nature Reserve on 15/04/2026 at 10:00.
+At least one visitor is registered in the waiting list.
+The first visitor on the waiting list received an available notification.</t>
+  </si>
+  <si>
+    <t>Spot is reserved for one hour</t>
+  </si>
+  <si>
+    <t>WaitingListSpotTransferredToNextVisitor</t>
+  </si>
+  <si>
+    <t>The system releases the reserved spot after one hour.
+The system transfers the available spot to the next visitor on the waiting list.
+The system sends an availability notification to the next visitor on the waiting list.</t>
+  </si>
+  <si>
+    <t>A spot became available for Banias Nature Reserve on 15/04/2026 at 10:00.
+At least two visitors are registered in the waiting list for Banias Nature Reserve on 15/04/2026 at 10:00.
+The first visitor on the waiting list received an available notification.
+The first visitor did not confirm the visit within one hour.</t>
+  </si>
+  <si>
+    <t>Spot is transferred to the next visitor after one hour</t>
+  </si>
+  <si>
+    <t>CancelExistingReservation</t>
+  </si>
+  <si>
+    <t>Open reservation management screen
+Enter visitor ID 
+Select an existing reservation for Banias Nature Reserve on 15/04/2026 at 10:00
+Click "cancel reservation" button</t>
+  </si>
+  <si>
+    <t>The system cancels the selected reservation
+The system displays a cancellation message
+The cancelled place become available in the system</t>
+  </si>
+  <si>
+    <t>The system in on the reservation management screen.
+A valid reservation for Banias Nature Reserve on 15/04/2026 at 10:00 exists in the system.</t>
+  </si>
+  <si>
+    <t>Cancellation of existing reservation</t>
+  </si>
+  <si>
+    <t>UniqueReservationIDGenerated</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 3
+Enter e-mail: visitor1@gmail.com
+Click "book visit" button
+Return to booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 16/04/2026 11:00
+Enter number of visitors: 2
+Enter e-mail: visitor2@gmail.com
+Click "book visit" button</t>
+  </si>
+  <si>
+    <t>The system generates a reservation ID for each reservation.
+Each reservation ID is unique.</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+Banias Nature Reserve has available capacity for each reservation.</t>
+  </si>
+  <si>
+    <t>Unique reservation ID generation</t>
+  </si>
+  <si>
+    <t>IdentificationUsingReservationID</t>
+  </si>
+  <si>
+    <t>Open reservation access screen
+Enter a valid reservation ID
+Click "identify" button</t>
+  </si>
+  <si>
+    <t>The system identifies the reservation.
+The system displays the reservation details for the entered reservation ID.</t>
+  </si>
+  <si>
+    <t>The system is on the reservation access screen.
+A valid reservation with a valid reservation ID exists in the system.</t>
+  </si>
+  <si>
+    <t>Identification using reservation ID</t>
+  </si>
+  <si>
+    <t>StoreNumberOfVisitsInReservation</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: 4
+Enter e-mail: visitor@gmail.com
+Click "book visit" button</t>
+  </si>
+  <si>
+    <t>The system creates a reservation for Banias Nature Reserve on 15/04/2026 at 10:00 for 4 visitors.
+The system adds 4 visitors to the reserved occupancy for Banias Nature Reserve on 15/04/2026 at 10:00.</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.
+Banias Nature Reserve has available capacity for 4 visitors on 15/04/2026 at 10:00.</t>
+  </si>
+  <si>
+    <t>Valid number of visitors is stored and counted for park occupancy</t>
+  </si>
+  <si>
+    <t>ReservationWithValidNumberOfVisitors</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 15/04/2026 10:00
+Enter number of visitors: -2
+Enter e-mail: visitor@gmail.com
+Click "book visit" button</t>
+  </si>
+  <si>
+    <t>The system does not creates a reservation.
+The system displays a message that the number of visitors is invalid.</t>
+  </si>
+  <si>
+    <t>The system is on the booking screen.</t>
+  </si>
+  <si>
+    <t>Invalid number of visitors</t>
+  </si>
+  <si>
+    <t>StoreVisitorsExitTime</t>
+  </si>
+  <si>
+    <t>Open park exit screen
+Enter visitor ID or scan QR code
+Click "confirm exit" button</t>
+  </si>
+  <si>
+    <t>The system records the visitors' exit time.
+The system updates the reservation status according to the exit.</t>
+  </si>
+  <si>
+    <t>The system is on the park exit screen.
+A valid active reservation exists in the system.
+The visitor have already entered the park.</t>
+  </si>
+  <si>
+    <t>Visitors' exit time is stored</t>
+  </si>
+  <si>
+    <t>CalculateCurrentNumberOfVisitorsInPark</t>
+  </si>
+  <si>
+    <t>Enter visitor ID for a reservation of 3 visitors
+Click "confirm entry" button
+Enter visitor ID for another reservation of 2 visitors
+Click "confirm entry" button
+Open park exit screen
+Enter visitor ID for a reservation of 2 visitors
+Click "confirm exit" button
+Open park status screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system displays that the current number of visitors in the park is 3.
+</t>
+  </si>
+  <si>
+    <t>The system is on the park entry screen.
+A valid reservation for 3 visitors exists in the system.
+Another valid reservation for 2 visitors exists in the system.
+After both reservations enter the park, 2 visitors are registered as exited</t>
+  </si>
+  <si>
+    <t>Calculate of current visitors in the park</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1463,14 +1833,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1490,7 +1860,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1498,15 +1868,28 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
@@ -1515,13 +1898,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1540,7 +1916,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1564,17 +1940,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1583,54 +1959,11 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1638,7 +1971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1653,50 +1986,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2017,19 +2356,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
   <dimension ref="A1:C83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="88.140625" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.4375" customWidth="1"/>
+    <col min="2" max="2" width="88.125" customWidth="1"/>
+    <col min="3" max="3" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="16" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:3" s="19" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="18" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="121.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="105.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2040,7 +2379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2051,7 +2390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2062,7 +2401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2073,7 +2412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2084,7 +2423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2095,7 +2434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2106,7 +2445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2117,7 +2456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2128,7 +2467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2139,7 +2478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2150,7 +2489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2161,7 +2500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2172,7 +2511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2183,7 +2522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2194,7 +2533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2205,7 +2544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2216,7 +2555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2227,7 +2566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2238,7 +2577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2249,7 +2588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2260,7 +2599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2271,7 +2610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2282,7 +2621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2293,7 +2632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2304,7 +2643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2315,7 +2654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2326,7 +2665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2337,7 +2676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2348,7 +2687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2359,7 +2698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2370,7 +2709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2381,7 +2720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2392,7 +2731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2403,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2414,7 +2753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2425,7 +2764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2436,7 +2775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2447,7 +2786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2458,7 +2797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2469,7 +2808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2480,7 +2819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2491,7 +2830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2502,7 +2841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2513,7 +2852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2524,7 +2863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2535,7 +2874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2546,7 +2885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2557,7 +2896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2568,7 +2907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2579,7 +2918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2590,7 +2929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2601,7 +2940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2612,7 +2951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2623,7 +2962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2634,7 +2973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2645,7 +2984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2656,7 +2995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2667,7 +3006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2678,7 +3017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2689,7 +3028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2700,7 +3039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2711,7 +3050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2722,7 +3061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2733,7 +3072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2744,7 +3083,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2755,7 +3094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2766,7 +3105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2777,7 +3116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2788,7 +3127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2799,7 +3138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2810,7 +3149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2821,7 +3160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2832,7 +3171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2843,7 +3182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>74</v>
       </c>
@@ -2854,7 +3193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>75</v>
       </c>
@@ -2865,7 +3204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>76</v>
       </c>
@@ -2876,7 +3215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>77</v>
       </c>
@@ -2887,7 +3226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>78</v>
       </c>
@@ -2898,7 +3237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>79</v>
       </c>
@@ -2909,7 +3248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>80</v>
       </c>
@@ -2931,1109 +3270,1378 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:Z62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z76"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="79.7109375" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="1" max="1" width="79.6875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="36.875" customWidth="1"/>
+    <col min="3" max="3" width="39.125" customWidth="1"/>
+    <col min="4" max="4" width="24.6875" customWidth="1"/>
+    <col min="5" max="5" width="31.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="16" customFormat="1" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" s="19" customFormat="1" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="18" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="11" spans="1:5" s="4" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="12" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    <row r="13" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="14" spans="1:5" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="15" spans="1:5" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="16" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B16" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="17" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+    <row r="18" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B18" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="19" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B19" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="20" spans="1:5" ht="108" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="21" spans="1:5" ht="67.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B21" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="22" spans="1:5" ht="67.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="23" spans="1:5" ht="67.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="24" spans="1:5" ht="162" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B24" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="25" spans="1:5" ht="162" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B25" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="88.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+    <row r="26" spans="1:5" ht="88.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E26" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+    <row r="27" spans="1:5" ht="75" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="157.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+    <row r="28" spans="1:5" ht="157.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E28" s="8" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="157.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+    <row r="29" spans="1:5" ht="157.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B29" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E29" s="8" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+    <row r="30" spans="1:5" ht="75" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E30" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="31" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E31" s="8" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+    <row r="32" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E32" s="8" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+    <row r="33" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E33" s="8" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+    <row r="34" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E34" s="8" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+    <row r="35" spans="1:26" ht="90" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E35" s="8" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+    <row r="36" spans="1:26" ht="90" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B36" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C36" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D36" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E36" s="8" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+    <row r="37" spans="1:26" ht="75" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C37" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D37" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E37" s="8" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+    <row r="38" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C38" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D38" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E38" s="8" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="136.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+    <row r="39" spans="1:26" ht="136.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B39" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C39" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D39" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E39" s="8" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="131.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+    <row r="40" spans="1:26" ht="131.44999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B40" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D40" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E40" s="8" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+    <row r="41" spans="1:26" ht="90" x14ac:dyDescent="0.35">
+      <c r="A41" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B41" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C41" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D41" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E41" s="8" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+    <row r="42" spans="1:26" ht="90" x14ac:dyDescent="0.35">
+      <c r="A42" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C42" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D42" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E42" s="8" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+    <row r="43" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C43" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D43" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E43" s="8" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+    <row r="44" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C44" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D44" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E44" s="8" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+    <row r="45" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C45" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D45" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E45" s="8" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+    <row r="46" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B46" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C46" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D46" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E46" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-    </row>
-    <row r="40" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+      <c r="Q46" s="14"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14"/>
+    </row>
+    <row r="47" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B47" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C47" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D47" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E47" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="13"/>
-      <c r="R40" s="13"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="13"/>
-      <c r="U40" s="13"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="13"/>
-      <c r="X40" s="13"/>
-      <c r="Y40" s="13"/>
-      <c r="Z40" s="13"/>
-    </row>
-    <row r="41" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+      <c r="Z47" s="14"/>
+    </row>
+    <row r="48" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B48" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C48" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D48" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E48" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="13"/>
-      <c r="Q41" s="13"/>
-      <c r="R41" s="13"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="13"/>
-      <c r="U41" s="13"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="13"/>
-      <c r="Z41" s="13"/>
-    </row>
-    <row r="42" spans="1:26" ht="169.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="14"/>
+      <c r="P48" s="14"/>
+      <c r="Q48" s="14"/>
+      <c r="R48" s="14"/>
+      <c r="S48" s="14"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="14"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="14"/>
+      <c r="X48" s="14"/>
+      <c r="Y48" s="14"/>
+      <c r="Z48" s="14"/>
+    </row>
+    <row r="49" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B49" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C49" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D49" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E49" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="13"/>
-      <c r="Q42" s="13"/>
-      <c r="R42" s="13"/>
-      <c r="S42" s="13"/>
-      <c r="T42" s="13"/>
-      <c r="U42" s="13"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="13"/>
-      <c r="X42" s="13"/>
-      <c r="Y42" s="13"/>
-      <c r="Z42" s="13"/>
-    </row>
-    <row r="43" spans="1:26" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+      <c r="P49" s="14"/>
+      <c r="Q49" s="14"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="14"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="14"/>
+      <c r="X49" s="14"/>
+      <c r="Y49" s="14"/>
+      <c r="Z49" s="14"/>
+    </row>
+    <row r="50" spans="1:26" ht="60" x14ac:dyDescent="0.35">
+      <c r="A50" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B50" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C50" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D50" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E50" s="11" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
+    <row r="51" spans="1:26" ht="45" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B51" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C51" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D51" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E51" s="11" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
+    <row r="52" spans="1:26" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B52" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C52" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D52" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E52" s="11" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19" t="s">
+    <row r="53" spans="1:26" ht="57.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B53" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C53" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D53" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E53" s="11" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19" t="s">
+    <row r="54" spans="1:26" ht="60" x14ac:dyDescent="0.35">
+      <c r="A54" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B54" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C54" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D54" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E54" s="11" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+    <row r="55" spans="1:26" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" ht="71.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" ht="75" x14ac:dyDescent="0.35">
+      <c r="A57" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" ht="60" x14ac:dyDescent="0.35">
+      <c r="A58" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" ht="136.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" ht="100.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="B48" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-    </row>
-    <row r="50" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E53" s="19" t="s">
+      <c r="B60" s="11" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="s">
+      <c r="C60" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="D60" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="E60" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="D54" s="20" t="s">
+    </row>
+    <row r="61" spans="1:26" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="B61" s="11" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
+      <c r="C61" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="D61" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="E61" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D55" s="20" t="s">
+    </row>
+    <row r="62" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="B62" s="11" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
+      <c r="C62" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="D62" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="E62" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="D56" s="20" t="s">
+    </row>
+    <row r="63" spans="1:26" ht="90" x14ac:dyDescent="0.35">
+      <c r="A63" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="B63" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-    </row>
-    <row r="58" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="19" t="s">
+      <c r="C63" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="D63" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="E63" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D58" s="20" t="s">
+    </row>
+    <row r="64" spans="1:26" ht="75" x14ac:dyDescent="0.35">
+      <c r="A64" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="B64" s="11" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
+      <c r="C64" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="D64" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="E64" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="D59" s="20" t="s">
+    </row>
+    <row r="65" spans="1:5" ht="86.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="B65" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-    </row>
-    <row r="61" spans="1:5" ht="126" x14ac:dyDescent="0.25">
-      <c r="A61" s="19" t="s">
+      <c r="D65" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="E65" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C61" s="20" t="s">
+    </row>
+    <row r="66" spans="1:5" ht="82.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="B66" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C66" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="D66" s="11" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="126" x14ac:dyDescent="0.25">
-      <c r="A62" s="19" t="s">
+      <c r="E66" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B62" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>342</v>
+    </row>
+    <row r="67" spans="1:5" ht="150" x14ac:dyDescent="0.35">
+      <c r="A67" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="195" x14ac:dyDescent="0.35">
+      <c r="A68" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="225" x14ac:dyDescent="0.35">
+      <c r="A69" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="A70" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="210" x14ac:dyDescent="0.35">
+      <c r="A71" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="A72" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="A73" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="A74" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="A75" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="165" x14ac:dyDescent="0.35">
+      <c r="A76" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shiraz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shiraz\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863D3C4A-FF0E-4DDF-A332-A3C49C38BC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ACBE46-AC7B-4193-8318-59AEB63D030F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="17287" windowHeight="11527" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
+    <workbookView xWindow="4313" yWindow="1013" windowWidth="17287" windowHeight="11527" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="427">
   <si>
     <t>Req. number</t>
   </si>
@@ -1809,6 +1809,9 @@
   </si>
   <si>
     <t>Calculate of current visitors in the park</t>
+  </si>
+  <si>
+    <t>:)</t>
   </si>
 </sst>
 </file>
@@ -2020,10 +2023,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2036,6 +2035,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2363,8 +2366,8 @@
     <col min="3" max="3" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="19" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:3" s="23" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>259</v>
       </c>
     </row>
@@ -3270,7 +3273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:Z76"/>
+  <dimension ref="A1:Z78"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="79.6875" style="17" customWidth="1"/>
@@ -3280,8 +3283,8 @@
     <col min="5" max="5" width="31.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="19" customFormat="1" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:5" s="23" customFormat="1" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>259</v>
       </c>
     </row>
@@ -3303,7 +3306,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="18" t="s">
         <v>344</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -3320,7 +3323,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>349</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -3337,7 +3340,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="18" t="s">
         <v>353</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -3354,7 +3357,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>357</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -3371,7 +3374,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>362</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -3388,7 +3391,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="18" t="s">
         <v>367</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -3405,7 +3408,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="18" t="s">
         <v>372</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -4487,7 +4490,7 @@
       <c r="D67" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="20" t="s">
         <v>381</v>
       </c>
     </row>
@@ -4504,7 +4507,7 @@
       <c r="D68" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="20" t="s">
         <v>386</v>
       </c>
     </row>
@@ -4521,7 +4524,7 @@
       <c r="D69" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="20" t="s">
         <v>390</v>
       </c>
     </row>
@@ -4538,7 +4541,7 @@
       <c r="D70" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="20" t="s">
         <v>395</v>
       </c>
     </row>
@@ -4555,11 +4558,11 @@
       <c r="D71" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="20" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="75" x14ac:dyDescent="0.35">
       <c r="A72" s="13" t="s">
         <v>401</v>
       </c>
@@ -4572,7 +4575,7 @@
       <c r="D72" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="20" t="s">
         <v>405</v>
       </c>
     </row>
@@ -4589,7 +4592,7 @@
       <c r="D73" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="20" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4603,10 +4606,10 @@
       <c r="C74" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="20" t="s">
         <v>415</v>
       </c>
     </row>
@@ -4617,13 +4620,13 @@
       <c r="B75" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="21" t="s">
         <v>418</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="20" t="s">
         <v>420</v>
       </c>
     </row>
@@ -4634,14 +4637,19 @@
       <c r="B76" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="21" t="s">
         <v>423</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="20" t="s">
         <v>425</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A78" s="17" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/G1_Acceptance.Ass1.xlsx
+++ b/G1_Acceptance.Ass1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shiraz\GoNature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\almo1\GoNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ACBE46-AC7B-4193-8318-59AEB63D030F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999B5D02-585E-4DB6-9575-AC4FB9226558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4313" yWindow="1013" windowWidth="17287" windowHeight="11527" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="446">
   <si>
     <t>Req. number</t>
   </si>
@@ -1011,16 +1011,6 @@
     <t>Average Stay Time Calculation for Park Visitors</t>
   </si>
   <si>
-    <t>Enter the park visit history screen.
-Choose the following visits:
-1. A group of 5 people spent 2 hours at the park
-2. 1 person spent 8 hours at the park
-Press "Calculate average stay time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The message "Average stay time calculated: 3 hours" will appear  on the screen </t>
-  </si>
-  <si>
     <t xml:space="preserve">A park exists in the system
 A few visits are recorded in the system (number of people and stay time for each reservation) </t>
   </si>
@@ -1127,11 +1117,6 @@
     <t>Entering the group leader's ID on exit marks the whole group is exited and decreases the total number of visitors accordingly</t>
   </si>
   <si>
-    <t>Check the available spots in the park
-Perform exit report
-Check the available spots in the park (again)</t>
-  </si>
-  <si>
     <t>The system accurately displays the number of visitors before the exit, and then after the group exits (e.g. 4 people) the number is decreased by 4.</t>
   </si>
   <si>
@@ -1195,16 +1180,6 @@
   </si>
   <si>
     <t>Pricing type 3 - frontal pay</t>
-  </si>
-  <si>
-    <t>Open booking screen
-Enter visitor ID
-Select park: Banias Nature Reserve
-Select date and time: 16/04/2026 11:00
-Enter number of visitors: 12
-Enter e-mail: guide@gmail.com
-Click "book visit" button
-(?) Click "Prepay" button (?)</t>
   </si>
   <si>
     <t>System generates a bill with 37% discount.
@@ -1347,96 +1322,6 @@
   </si>
   <si>
     <t>check if the system correctly caculates stay duration upon exit</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Open "Entrance Management" screen
-Click "Individual/Family visit" button
-Enter reservation ID
-Click "Confirm Entry" button
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Open visitor log or database record (?)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Open "Exit Management" screen
-Click "Individual/Family visit" button
-Enter reservation ID
-Click "Confirm Exit" button
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Open visitor log or database record (?)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(?)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CheckOccupancy_AfterExit</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">GenerateBill_PrebookedGroup_Prepay 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(לא בטוח לגבי זה)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">GenerateBill_CasualGroup
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>לא סגור אם זה אפשרי בכלל בסיפור אבל נראלי שכן כי לא כתוב שלא (או ספספתי)</t>
-    </r>
   </si>
   <si>
     <t>BookVisitSuccessful_Available</t>
@@ -1463,19 +1348,8 @@
     <t>Regular visitor booking</t>
   </si>
   <si>
-    <t>BookVisitUnsuccessful_NotAvailable</t>
-  </si>
-  <si>
-    <t>The system informs the user that no space is available for selected visit time.
-The system does not create a reservation.
-The system allows the user to choose another date or join the waiting list.</t>
-  </si>
-  <si>
     <t>The system is on the booking screen.
 Banias Nature Reserve has no available capacity for 3 visitors on 15/04/2026 at 10:00.</t>
-  </si>
-  <si>
-    <t>Park is fully booked</t>
   </si>
   <si>
     <t>BookVisitWaitingList</t>
@@ -1811,14 +1685,175 @@
     <t>Calculate of current visitors in the park</t>
   </si>
   <si>
-    <t>:)</t>
+    <t>Open login page.
+Click "Visitor Log In" button.
+Enter ID number: 1234
+Click "Log In" button.</t>
+  </si>
+  <si>
+    <t>The system does not log the vistor in.</t>
+  </si>
+  <si>
+    <t>IdentificationUnsuccessful_AsNonEmployee_InvalidID</t>
+  </si>
+  <si>
+    <t>Regular visitor log in using ID number.</t>
+  </si>
+  <si>
+    <t>The system is on the log in page.
+The ID is not valid</t>
+  </si>
+  <si>
+    <t>Check the available spots in the park
+Report exit of the number of people exited
+Check the available spots in the park (again)</t>
+  </si>
+  <si>
+    <t>CheckOccupancy_AfterExit</t>
+  </si>
+  <si>
+    <t>ReportExit_0Visitors</t>
+  </si>
+  <si>
+    <t>Open "Occupancy Management" screen
+Enter number of exiting visitors: 0
+Click "Report Exit"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee is logged in.
+</t>
+  </si>
+  <si>
+    <t>Trying to report 0 people exiting</t>
+  </si>
+  <si>
+    <t>ReportExit_Unsuccessful_NegativeVisitors</t>
+  </si>
+  <si>
+    <t>Open "Occupancy Management" screen
+Enter number of exiting visitors: -4
+Click "Report Exit"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system displays the message "0 visitors selected. Please try again".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system displays the message "Negative visitors selected. Please try again".
+</t>
+  </si>
+  <si>
+    <t>Trying to enter a negative value</t>
+  </si>
+  <si>
+    <t>ReportExit_Unsuccessful_NegativeOccupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee is logged in.
+There are 3 or less visitors in the park
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system displays the message "Invalid input. Negative visitors left in the park. Please try again".
+</t>
+  </si>
+  <si>
+    <t>Trying to enter a value larger than visitors in the park</t>
+  </si>
+  <si>
+    <t>Open booking screen
+Enter visitor ID
+Select park: Banias Nature Reserve
+Select date and time: 16/04/2026 11:00
+Enter number of visitors: 12
+Enter e-mail: guide@gmail.com
+Click "book visit" button
+Click "Prepay" button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenerateBill_PrebookedGroup_Prepay 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenerateBill_CasualOrganizedGroup
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open "Entrance Management" screen
+Click "Individual/Family visit" button
+Enter reservation ID
+Click "Confirm Entry" button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Open visitor log or database record</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open "Exit Management" screen
+Click "Individual/Family visit" button
+Enter reservation ID
+Click "Confirm Exit" button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Open visitor log or database record</t>
+    </r>
+  </si>
+  <si>
+    <t>Enter the park visit history screen.
+Choose the following visits:
+1. A group of 5 people spent 2 hours at the park
+2. 1 person spent 8 hours at the park
+Press "Calculate average stay time"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The message "Average stay time calculated: 3 hours" will appear on the screen </t>
+  </si>
+  <si>
+    <t>BookVisitUnsuccessful_QoutaReached</t>
+  </si>
+  <si>
+    <t>The system informs the user that no space is available for selected visit time.
+The system does not create a reservation.
+The system allows the user to see the reservation table in order to choose another date or join the waiting list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system is on the booking screen.
+Banias Nature Reserve has no available capacity for 3 visitors on 15/04/2026 at 10:00.
+Banias Nature Reserve's capacity: 1000
+Qouta- capacity gap: 200
+There are already 800 spots booked for the mentioned time at the park </t>
+  </si>
+  <si>
+    <t>Bookings quota reached</t>
+  </si>
+  <si>
+    <t>Group #1, members: 
+Bar Sagi, bar.sagi@e.braude.ac.il
+Shiraz Shamai, shiraz.shamai@e.braude.ac.il
+Gal Dolev, gal.dolev@e.braude.ac.il
+Reut Dahan, reut.dahan@e.braude.ac.il
+date: 09/04/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1831,14 +1866,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1861,13 +1888,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
@@ -1877,24 +1897,15 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1903,6 +1914,7 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1974,71 +1986,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2062,7 +2055,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -2359,19 +2352,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
   <dimension ref="A1:C83"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.4375" customWidth="1"/>
+    <col min="1" max="1" width="9.5" customWidth="1"/>
     <col min="2" max="2" width="88.125" customWidth="1"/>
     <col min="3" max="3" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="105.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="93.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="120.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2382,40 +2375,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
+    <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2426,7 +2419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2437,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2448,7 +2441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2459,7 +2452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2470,7 +2463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2481,7 +2474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2492,7 +2485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2503,7 +2496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2514,7 +2507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2525,7 +2518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2536,7 +2529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2547,8 +2540,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <v>16</v>
       </c>
       <c r="B18" t="s">
@@ -2558,7 +2551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2569,7 +2562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2580,7 +2573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2591,7 +2584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2602,7 +2595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2613,7 +2606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2624,7 +2617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2635,7 +2628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2646,7 +2639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2657,7 +2650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2668,7 +2661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2679,7 +2672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2690,7 +2683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2701,7 +2694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2712,7 +2705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2723,7 +2716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2734,7 +2727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2745,7 +2738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2756,7 +2749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2767,7 +2760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2778,7 +2771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2789,7 +2782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2800,7 +2793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2811,7 +2804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2822,7 +2815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2833,7 +2826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2844,7 +2837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2855,7 +2848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2866,7 +2859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2877,7 +2870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2888,7 +2881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2899,7 +2892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2910,7 +2903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2921,7 +2914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2932,7 +2925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2943,7 +2936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2954,7 +2947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2965,7 +2958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2976,7 +2969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2987,7 +2980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2998,7 +2991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>57</v>
       </c>
@@ -3009,7 +3002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>58</v>
       </c>
@@ -3020,7 +3013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>59</v>
       </c>
@@ -3031,7 +3024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>60</v>
       </c>
@@ -3042,7 +3035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
@@ -3053,7 +3046,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
@@ -3064,7 +3057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
@@ -3075,7 +3068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
@@ -3086,7 +3079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>65</v>
       </c>
@@ -3097,7 +3090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>66</v>
       </c>
@@ -3108,7 +3101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>67</v>
       </c>
@@ -3119,7 +3112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>68</v>
       </c>
@@ -3130,7 +3123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>69</v>
       </c>
@@ -3141,7 +3134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>70</v>
       </c>
@@ -3152,7 +3145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>71</v>
       </c>
@@ -3163,7 +3156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>72</v>
       </c>
@@ -3174,7 +3167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>73</v>
       </c>
@@ -3185,7 +3178,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>74</v>
       </c>
@@ -3196,7 +3189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>75</v>
       </c>
@@ -3207,7 +3200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>76</v>
       </c>
@@ -3218,7 +3211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>77</v>
       </c>
@@ -3229,7 +3222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>78</v>
       </c>
@@ -3240,7 +3233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>79</v>
       </c>
@@ -3251,7 +3244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>80</v>
       </c>
@@ -3273,1383 +3266,1363 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A028A801-0122-4DDE-8D73-57AF100E1B01}">
-  <dimension ref="A1:Z78"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="79.6875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="36.875" customWidth="1"/>
-    <col min="3" max="3" width="39.125" customWidth="1"/>
-    <col min="4" max="4" width="24.6875" customWidth="1"/>
-    <col min="5" max="5" width="31.75" customWidth="1"/>
+    <col min="1" max="1" width="79.75" style="14" customWidth="1"/>
+    <col min="2" max="2" width="36.875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="39.125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="38.625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="23" customFormat="1" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:5" s="15" customFormat="1" ht="96.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="16" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="195" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="195" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="165" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="165" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="165" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="165" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="C51" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="75" x14ac:dyDescent="0.2">
+      <c r="A70" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="B71" s="4" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="C71" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="D71" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="E71" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D8" s="11" t="s">
+    </row>
+    <row r="72" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="B72" s="4" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="C72" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="D72" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="E72" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="D9" s="11" t="s">
+    </row>
+    <row r="73" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="B73" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="4" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="94.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="108" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="67.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="67.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="67.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="162" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="162" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="88.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="75" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="157.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="157.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="75" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="90" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="90" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" ht="90" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" ht="90" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" ht="75" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" ht="136.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" ht="131.44999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" ht="90" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" ht="90" x14ac:dyDescent="0.35">
-      <c r="A42" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="14"/>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="14"/>
-      <c r="Z46" s="14"/>
-    </row>
-    <row r="47" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="14"/>
-      <c r="S47" s="14"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="14"/>
-      <c r="W47" s="14"/>
-      <c r="X47" s="14"/>
-      <c r="Y47" s="14"/>
-      <c r="Z47" s="14"/>
-    </row>
-    <row r="48" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="14"/>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="14"/>
-      <c r="W48" s="14"/>
-      <c r="X48" s="14"/>
-      <c r="Y48" s="14"/>
-      <c r="Z48" s="14"/>
-    </row>
-    <row r="49" spans="1:26" ht="169.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="14"/>
-      <c r="S49" s="14"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="14"/>
-      <c r="W49" s="14"/>
-      <c r="X49" s="14"/>
-      <c r="Y49" s="14"/>
-      <c r="Z49" s="14"/>
-    </row>
-    <row r="50" spans="1:26" ht="60" x14ac:dyDescent="0.35">
-      <c r="A50" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" ht="45" x14ac:dyDescent="0.35">
-      <c r="A51" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" ht="57.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" ht="60" x14ac:dyDescent="0.35">
-      <c r="A54" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" ht="71.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" ht="75" x14ac:dyDescent="0.35">
-      <c r="A57" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" ht="60" x14ac:dyDescent="0.35">
-      <c r="A58" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" ht="136.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" ht="100.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26" ht="90" x14ac:dyDescent="0.35">
-      <c r="A63" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26" ht="75" x14ac:dyDescent="0.35">
-      <c r="A64" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="86.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="82.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="150" x14ac:dyDescent="0.35">
-      <c r="A67" s="13" t="s">
+      <c r="D73" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="E73" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C67" s="8" t="s">
+    </row>
+    <row r="74" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="B74" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="C74" s="4" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="195" x14ac:dyDescent="0.35">
-      <c r="A68" s="13" t="s">
+      <c r="D74" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="E74" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C68" s="8" t="s">
+    </row>
+    <row r="75" spans="1:5" ht="210" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="C75" s="4" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="225" x14ac:dyDescent="0.35">
-      <c r="A69" s="13" t="s">
+      <c r="D75" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="C69" s="8" t="s">
+      <c r="E75" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D69" s="8" t="s">
+    </row>
+    <row r="76" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A76" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="B76" s="4" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="105" x14ac:dyDescent="0.35">
-      <c r="A70" s="13" t="s">
+      <c r="C76" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="D76" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="E76" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D70" s="8" t="s">
+    </row>
+    <row r="77" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A77" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="E70" s="20" t="s">
+      <c r="B77" s="7" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="210" x14ac:dyDescent="0.35">
-      <c r="A71" s="13" t="s">
+      <c r="C77" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="D77" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="E77" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="D71" s="8" t="s">
+    </row>
+    <row r="78" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="E71" s="20" t="s">
+      <c r="B78" s="7" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="75" x14ac:dyDescent="0.35">
-      <c r="A72" s="13" t="s">
+      <c r="C78" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="D78" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="E78" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D72" s="8" t="s">
+    </row>
+    <row r="79" spans="1:5" ht="60" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="B79" s="4" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="105" x14ac:dyDescent="0.35">
-      <c r="A73" s="13" t="s">
+      <c r="C79" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="D79" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="E79" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D73" s="8" t="s">
+    </row>
+    <row r="80" spans="1:5" ht="165" x14ac:dyDescent="0.2">
+      <c r="A80" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="B80" s="4" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="105" x14ac:dyDescent="0.35">
-      <c r="A74" s="13" t="s">
+      <c r="C80" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="D80" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="E80" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="90" x14ac:dyDescent="0.35">
-      <c r="A75" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="165" x14ac:dyDescent="0.35">
-      <c r="A76" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="E76" s="20" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A78" s="17" t="s">
-        <v>426</v>
       </c>
     </row>
   </sheetData>
